--- a/utils/po_templates/po_template.xlsx
+++ b/utils/po_templates/po_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\utils\po_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6011DA87-2291-476A-89C5-286AC5F6559E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AA6282-043A-46CB-B6DA-94F883965C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -123,10 +123,11 @@
     <t>TBP</t>
   </si>
   <si>
-    <t>*** Important notes go here. ***</t>
-  </si>
-  <si>
     <t>Stickers</t>
+  </si>
+  <si>
+    <t>*** The export box supplied by Toyota should never be opened unless specific instructions from CPS Africa are given to do so.
+Your entity will be held responsible if you fail to comply ***</t>
   </si>
 </sst>
 </file>
@@ -729,11 +730,59 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -741,164 +790,116 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -968,6 +969,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>536736</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>80459</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03D1343F-7E8B-476E-AFF2-B560CAE9DE68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="139390" y="0"/>
+          <a:ext cx="2743748" cy="568325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1260,12 +1310,12 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="84" t="s">
+      <c r="K1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E2" s="6"/>
@@ -1274,10 +1324,10 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E3" s="6"/>
@@ -1293,88 +1343,88 @@
       <c r="O3" s="6"/>
     </row>
     <row r="4" spans="1:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K4" s="93" t="s">
+      <c r="K4" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="42"/>
+      <c r="C5" s="56"/>
       <c r="D5" s="20"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="10"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="94"/>
-      <c r="C6" s="94"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
       <c r="D6" s="29"/>
       <c r="E6" s="30"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="4"/>
-      <c r="K6" s="91" t="s">
+      <c r="K6" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="97"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="29"/>
       <c r="E7" s="30"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="4"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="43"/>
+      <c r="N7" s="43"/>
     </row>
     <row r="8" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="29"/>
       <c r="E8" s="30"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="4"/>
-      <c r="K8" s="75" t="s">
+      <c r="K8" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="97"/>
-      <c r="M8" s="97"/>
-      <c r="N8" s="97"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
+      <c r="N8" s="57"/>
     </row>
     <row r="9" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="29"/>
       <c r="E9" s="30"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="4"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="86"/>
-      <c r="N9" s="86"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
     </row>
     <row r="10" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="7"/>
@@ -1405,75 +1455,75 @@
       <c r="B12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
       <c r="F12" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="80" t="s">
+      <c r="G12" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
       <c r="J12" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="80" t="s">
+      <c r="K12" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
       <c r="N12" s="36" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="38"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="89"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="46"/>
       <c r="F13" s="26"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="83"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="48"/>
       <c r="J13" s="35"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="67"/>
       <c r="N13" s="35"/>
     </row>
     <row r="14" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="39"/>
-      <c r="C14" s="87"/>
-      <c r="D14" s="88"/>
-      <c r="E14" s="89"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46"/>
       <c r="F14" s="26"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="88"/>
-      <c r="I14" s="88"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
       <c r="J14" s="35"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
       <c r="N14" s="37"/>
     </row>
     <row r="15" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="40"/>
-      <c r="C15" s="87"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="89"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="46"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="83"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="48"/>
       <c r="J15" s="35"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
       <c r="N15" s="37"/>
     </row>
     <row r="16" spans="1:15" s="7" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -1507,277 +1557,277 @@
       <c r="N17"/>
     </row>
     <row r="18" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
       <c r="H18" s="25"/>
-      <c r="I18" s="41" t="s">
+      <c r="I18" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="J18" s="41" t="s">
+      <c r="J18" s="65" t="s">
         <v>11</v>
       </c>
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="41" t="s">
+      <c r="L18" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="78" t="s">
+      <c r="M18" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="78"/>
+      <c r="N18" s="63"/>
     </row>
     <row r="19" spans="2:14" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
       <c r="H19" s="25"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="31">
         <v>65</v>
       </c>
-      <c r="L19" s="42"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="79"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
     </row>
     <row r="20" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
       <c r="K20" s="23"/>
       <c r="L20" s="23"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
+      <c r="M20" s="59"/>
+      <c r="N20" s="59"/>
     </row>
     <row r="21" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
       <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
     </row>
     <row r="22" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="32"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
       <c r="I22" s="21"/>
       <c r="J22" s="21"/>
       <c r="K22" s="23"/>
       <c r="L22" s="23"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="59"/>
     </row>
     <row r="23" spans="2:14" s="7" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="33"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="59"/>
     </row>
     <row r="24" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="2:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
+      <c r="B25" s="97"/>
+      <c r="C25" s="97"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="97"/>
     </row>
     <row r="26" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
       <c r="H27" s="20"/>
-      <c r="K27" s="41" t="s">
+      <c r="K27" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="L27" s="41"/>
+      <c r="L27" s="65"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="59"/>
+      <c r="C28" s="81"/>
       <c r="D28" s="13"/>
-      <c r="E28" s="61" t="s">
+      <c r="E28" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
       <c r="H28" s="17"/>
-      <c r="K28" s="53" t="s">
+      <c r="K28" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="L28" s="56">
+      <c r="L28" s="78">
         <f>SUM(L20:L23)</f>
         <v>0</v>
       </c>
       <c r="N28" s="24"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B29" s="60"/>
-      <c r="C29" s="60"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
       <c r="D29" s="14"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
       <c r="H29" s="17"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="57"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="79"/>
     </row>
     <row r="30" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="64"/>
+      <c r="C30" s="86"/>
       <c r="D30" s="13"/>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="83"/>
       <c r="H30" s="18"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="58"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="80"/>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="63"/>
-      <c r="C31" s="64"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="86"/>
       <c r="D31" s="14"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
       <c r="H31" s="18"/>
-      <c r="K31" s="53" t="s">
+      <c r="K31" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="L31" s="66"/>
+      <c r="L31" s="88"/>
     </row>
     <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="59"/>
+      <c r="C32" s="81"/>
       <c r="D32" s="13"/>
-      <c r="E32" s="73" t="s">
+      <c r="E32" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
+      <c r="F32" s="95"/>
+      <c r="G32" s="95"/>
       <c r="H32" s="8"/>
-      <c r="K32" s="54"/>
-      <c r="L32" s="67"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="89"/>
     </row>
     <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="60"/>
-      <c r="C33" s="60"/>
+      <c r="B33" s="82"/>
+      <c r="C33" s="82"/>
       <c r="D33" s="14"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="96"/>
       <c r="H33" s="8"/>
-      <c r="K33" s="55"/>
-      <c r="L33" s="68"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="90"/>
     </row>
     <row r="34" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="69"/>
+      <c r="B34" s="91" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="91"/>
       <c r="D34" s="16"/>
-      <c r="E34" s="71" t="s">
+      <c r="E34" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
+      <c r="F34" s="93"/>
+      <c r="G34" s="93"/>
       <c r="H34" s="8"/>
-      <c r="K34" s="53" t="s">
+      <c r="K34" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="L34" s="66">
+      <c r="L34" s="88">
         <f>L28</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
+      <c r="B35" s="92"/>
+      <c r="C35" s="92"/>
       <c r="D35" s="15"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="94"/>
+      <c r="G35" s="94"/>
       <c r="H35" s="8"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="67"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="89"/>
     </row>
     <row r="36" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
+      <c r="B36" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="71"/>
       <c r="H36" s="19"/>
       <c r="J36" s="11"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="68"/>
+      <c r="K36" s="77"/>
+      <c r="L36" s="90"/>
     </row>
     <row r="37" spans="2:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="50"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="52"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="74"/>
       <c r="H37" s="19"/>
       <c r="K37" s="12"/>
       <c r="L37" s="12"/>
@@ -1835,15 +1885,54 @@
     <row r="47" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="50" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I50" s="46" t="s">
+      <c r="I50" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
+      <c r="J50" s="68"/>
+      <c r="K50" s="68"/>
+      <c r="L50" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="B36:G37"/>
+    <mergeCell ref="K28:K30"/>
+    <mergeCell ref="L28:L30"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="L31:L33"/>
+    <mergeCell ref="K31:K33"/>
+    <mergeCell ref="K34:K36"/>
+    <mergeCell ref="L34:L36"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="E34:G35"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="E32:G33"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="M18:N19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="C18:G19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="G13:I13"/>
     <mergeCell ref="K1:N2"/>
     <mergeCell ref="L4:N5"/>
     <mergeCell ref="C15:E15"/>
@@ -1860,45 +1949,6 @@
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="L6:N7"/>
     <mergeCell ref="L8:N9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="M18:N19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="C18:G19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="B36:G37"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="L28:L30"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="L31:L33"/>
-    <mergeCell ref="K31:K33"/>
-    <mergeCell ref="K34:K36"/>
-    <mergeCell ref="L34:L36"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="C21:H21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="F13:F15">
@@ -1921,6 +1971,7 @@
     <oddFooter>&amp;C_________________________________________________________________________________________
 CPS AFRICA NV - Bijkhoevelaan 12 - 2110 Wijnegem - VAT BE0578.970.135</oddFooter>
   </headerFooter>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1934,16 +1985,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4AD7773B4E3EE4CA44A107277FDE460" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="efb4862029cda6bc99e117f09e819a98">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a52bf194-6401-462b-9261-416d3ab8d515" xmlns:ns3="5178cd30-2d2c-4c09-880d-a5cc10f48446" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce9f932dd84aa414e8242018441c5ce8" ns2:_="" ns3:_="">
     <xsd:import namespace="a52bf194-6401-462b-9261-416d3ab8d515"/>
@@ -2172,6 +2213,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a52bf194-6401-462b-9261-416d3ab8d515">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73DC9C3-8993-467B-9C7F-6F901699B4B8}">
   <ds:schemaRefs>
@@ -2181,16 +2232,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57ECAF93-D10D-495E-AE39-418217FB97DF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2207,4 +2248,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B752BE4-1396-4BCB-B02F-A8A256B5B09D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a52bf194-6401-462b-9261-416d3ab8d515"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/utils/po_templates/po_template.xlsx
+++ b/utils/po_templates/po_template.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\utils\po_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AA6282-043A-46CB-B6DA-94F883965C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149D4FF2-B778-47D6-B44C-E80F59AD32F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$N$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$N$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -614,7 +614,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -897,9 +897,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1286,7 +1283,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="2" customWidth="1"/>
@@ -1663,171 +1660,171 @@
       <c r="N23" s="59"/>
     </row>
     <row r="24" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="2:14" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="97"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="97"/>
-    </row>
-    <row r="26" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+    <row r="25" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="20"/>
-      <c r="K27" s="65" t="s">
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="20"/>
+      <c r="K26" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="L27" s="65"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="81" t="s">
+      <c r="L26" s="65"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B27" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="81"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="83" t="s">
+      <c r="C27" s="81"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="17"/>
-      <c r="K28" s="75" t="s">
+      <c r="F27" s="83"/>
+      <c r="G27" s="83"/>
+      <c r="H27" s="17"/>
+      <c r="K27" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="L28" s="78">
+      <c r="L27" s="78">
         <f>SUM(L20:L23)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="24"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B29" s="82"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="84"/>
-      <c r="H29" s="17"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="79"/>
-    </row>
-    <row r="30" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="85" t="s">
+      <c r="N27" s="24"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B28" s="82"/>
+      <c r="C28" s="82"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="17"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="79"/>
+    </row>
+    <row r="29" spans="2:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="85" t="s">
         <v>17</v>
       </c>
+      <c r="C29" s="86"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="18"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="80"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30" s="85"/>
       <c r="C30" s="86"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="87" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
       <c r="H30" s="18"/>
-      <c r="K30" s="77"/>
-      <c r="L30" s="80"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="85"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84"/>
-      <c r="H31" s="18"/>
-      <c r="K31" s="75" t="s">
+      <c r="K30" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="L31" s="88"/>
-    </row>
-    <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="81" t="s">
+      <c r="L30" s="88"/>
+    </row>
+    <row r="31" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="81"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="95" t="s">
+      <c r="C31" s="81"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="95"/>
-      <c r="G32" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="8"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="89"/>
+    </row>
+    <row r="32" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="82"/>
+      <c r="C32" s="82"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
       <c r="H32" s="8"/>
-      <c r="K32" s="76"/>
-      <c r="L32" s="89"/>
-    </row>
-    <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="82"/>
-      <c r="C33" s="82"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="90"/>
+    </row>
+    <row r="33" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="91" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="91"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
       <c r="H33" s="8"/>
-      <c r="K33" s="77"/>
-      <c r="L33" s="90"/>
-    </row>
-    <row r="34" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="91" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="91"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="93"/>
-      <c r="G34" s="93"/>
+      <c r="K33" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" s="88">
+        <f>L27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
       <c r="H34" s="8"/>
-      <c r="K34" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="L34" s="88">
-        <f>L28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="92"/>
-      <c r="C35" s="92"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
-      <c r="G35" s="94"/>
-      <c r="H35" s="8"/>
-      <c r="K35" s="76"/>
-      <c r="L35" s="89"/>
-    </row>
-    <row r="36" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="69" t="s">
+      <c r="K34" s="76"/>
+      <c r="L34" s="89"/>
+    </row>
+    <row r="35" spans="2:14" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="71"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="19"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="90"/>
+    </row>
+    <row r="36" spans="2:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="72"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="74"/>
       <c r="H36" s="19"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="77"/>
-      <c r="L36" s="90"/>
-    </row>
-    <row r="37" spans="2:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="72"/>
-      <c r="C37" s="73"/>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="74"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+    </row>
+    <row r="37" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
       <c r="H37" s="19"/>
       <c r="K37" s="12"/>
       <c r="L37" s="12"/>
@@ -1854,75 +1851,63 @@
       <c r="K39" s="12"/>
       <c r="L39" s="12"/>
     </row>
-    <row r="40" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-    </row>
-    <row r="41" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="N41" s="12"/>
-    </row>
+    <row r="40" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="N40" s="12"/>
+    </row>
+    <row r="41" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="42" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="43" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N45" s="12"/>
-    </row>
+    <row r="44" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N44" s="12"/>
+    </row>
+    <row r="45" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="46" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="47" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I50" s="68" t="s">
+    <row r="49" spans="9:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I49" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="J50" s="68"/>
-      <c r="K50" s="68"/>
-      <c r="L50" s="68"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="68"/>
+      <c r="L49" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="B27:G27"/>
+  <mergeCells count="54">
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="M22:N22"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="M23:N23"/>
-    <mergeCell ref="B25:J25"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="M20:N20"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="B36:G37"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="L28:L30"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="B30:C31"/>
-    <mergeCell ref="E30:G31"/>
-    <mergeCell ref="L31:L33"/>
-    <mergeCell ref="K31:K33"/>
-    <mergeCell ref="K34:K36"/>
-    <mergeCell ref="L34:L36"/>
-    <mergeCell ref="B34:C35"/>
-    <mergeCell ref="E34:G35"/>
-    <mergeCell ref="B32:C33"/>
-    <mergeCell ref="E32:G33"/>
-    <mergeCell ref="K8:K9"/>
     <mergeCell ref="M21:N21"/>
     <mergeCell ref="C22:H22"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="B35:G36"/>
+    <mergeCell ref="K27:K29"/>
+    <mergeCell ref="L27:L29"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="E27:G28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="E29:G30"/>
+    <mergeCell ref="L30:L32"/>
+    <mergeCell ref="K30:K32"/>
+    <mergeCell ref="K33:K35"/>
+    <mergeCell ref="L33:L35"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="E33:G34"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="E31:G32"/>
+    <mergeCell ref="K8:K9"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="M18:N19"/>
     <mergeCell ref="L18:L19"/>
